--- a/averaged_runsNorESM_copy.xlsx
+++ b/averaged_runsNorESM_copy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/JohnMatthew/Downloads/Thorne_15_codefigurestats/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_8FF1F33761677F2D4391D99530293AD58432DA59" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{893408AA-1CBB-1F47-A0CA-78081D7E7FCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="940" yWindow="4260" windowWidth="28380" windowHeight="15100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2720" yWindow="3080" windowWidth="28380" windowHeight="15100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="averaged_runsVolc" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="118">
   <si>
     <t>method_name</t>
   </si>
@@ -386,6 +386,9 @@
   <si>
     <t>CGWL10y_sUKCP</t>
   </si>
+  <si>
+    <t>(failed SSP cutoff)</t>
+  </si>
 </sst>
 </file>
 
@@ -426,10 +429,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -764,10 +768,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AV61"/>
+  <dimension ref="A1:AX61"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -910,7 +914,7 @@
         <v>7.6999999999999999E-2</v>
       </c>
     </row>
-    <row r="2" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>45</v>
       </c>
@@ -1055,7 +1059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>48</v>
       </c>
@@ -1200,7 +1204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>49</v>
       </c>
@@ -1344,8 +1348,11 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
+      <c r="AX4" s="3" t="s">
+        <v>117</v>
+      </c>
     </row>
-    <row r="5" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>50</v>
       </c>
@@ -1490,7 +1497,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>51</v>
       </c>
@@ -1635,7 +1642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>53</v>
       </c>
@@ -1780,7 +1787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>54</v>
       </c>
@@ -1925,7 +1932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>55</v>
       </c>
@@ -2070,7 +2077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>56</v>
       </c>
@@ -2215,7 +2222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>57</v>
       </c>
@@ -2360,7 +2367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>58</v>
       </c>
@@ -2505,7 +2512,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>59</v>
       </c>
@@ -2650,7 +2657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>61</v>
       </c>
@@ -2795,7 +2802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>62</v>
       </c>
@@ -2940,7 +2947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>63</v>
       </c>
@@ -3955,147 +3962,147 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
+    <row r="23" spans="1:48" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D23">
+      <c r="D23" s="3">
         <v>11.03333333333333</v>
       </c>
-      <c r="E23">
+      <c r="E23" s="3">
         <v>31.033333333333331</v>
       </c>
-      <c r="F23">
+      <c r="F23" s="3">
         <v>7.2959300765283999E-3</v>
       </c>
-      <c r="G23">
+      <c r="G23" s="3">
         <v>58.767822079472232</v>
       </c>
-      <c r="H23">
+      <c r="H23" s="3">
         <v>6.8750000144594495E-2</v>
       </c>
-      <c r="I23">
+      <c r="I23" s="3">
         <v>-1.054629629459555</v>
       </c>
-      <c r="J23">
+      <c r="J23" s="3">
         <v>-0.49793036808040991</v>
       </c>
-      <c r="K23">
+      <c r="K23" s="3">
         <v>-0.79305555541018291</v>
       </c>
-      <c r="L23">
+      <c r="L23" s="3">
         <v>-1.8138888887190809</v>
       </c>
-      <c r="M23">
+      <c r="M23" s="3">
         <v>-0.47777777763268808</v>
       </c>
-      <c r="N23">
+      <c r="N23" s="3">
         <v>-1.6152777776081471</v>
       </c>
-      <c r="O23">
+      <c r="O23" s="3">
         <v>2.8400121143873451</v>
       </c>
-      <c r="P23">
+      <c r="P23" s="3">
         <v>5.3830433285238302E-2</v>
       </c>
-      <c r="Q23">
+      <c r="Q23" s="3">
         <v>-7.3649440143140003E-4</v>
       </c>
-      <c r="R23">
+      <c r="R23" s="3">
         <v>1.96999569733937E-2</v>
       </c>
-      <c r="S23">
+      <c r="S23" s="3">
         <v>7.2958611547567003E-3</v>
       </c>
-      <c r="T23">
+      <c r="T23" s="3">
         <v>-120.1548585993613</v>
       </c>
-      <c r="U23">
+      <c r="U23" s="3">
         <v>0.3076388890333267</v>
       </c>
-      <c r="V23">
+      <c r="V23" s="3">
         <v>-1.386574073905577</v>
       </c>
-      <c r="W23">
+      <c r="W23" s="3">
         <v>-0.55827991437078694</v>
       </c>
-      <c r="X23">
+      <c r="X23" s="3">
         <v>-0.55416666652145063</v>
       </c>
-      <c r="Y23">
+      <c r="Y23" s="3">
         <v>-1.9416666664976681</v>
       </c>
-      <c r="Z23">
+      <c r="Z23" s="3">
         <v>1.116666666810374</v>
       </c>
-      <c r="AA23">
+      <c r="AA23" s="3">
         <v>-1.1041666664984251</v>
       </c>
-      <c r="AB23">
+      <c r="AB23" s="3">
         <v>2.8746616808612488</v>
       </c>
-      <c r="AC23">
+      <c r="AC23" s="3">
         <v>1.9699887313186601E-2</v>
       </c>
-      <c r="AD23">
+      <c r="AD23" s="3">
         <v>4.9148641385569949</v>
       </c>
-      <c r="AE23">
+      <c r="AE23" s="3">
         <v>2.5558078144581922</v>
       </c>
-      <c r="AF23">
+      <c r="AF23" s="3">
         <v>6.8741101232095652</v>
       </c>
-      <c r="AG23">
+      <c r="AG23" s="3">
         <v>5.5101174725624729</v>
       </c>
-      <c r="AH23">
+      <c r="AH23" s="3">
         <v>1.168130746063736</v>
       </c>
-      <c r="AI23">
+      <c r="AI23" s="3">
         <v>14.92333333333333</v>
       </c>
-      <c r="AJ23">
+      <c r="AJ23" s="3">
         <v>14.80666666666667</v>
       </c>
-      <c r="AK23">
+      <c r="AK23" s="3">
         <v>5.18167282574283E-2</v>
       </c>
-      <c r="AL23">
+      <c r="AL23" s="3">
         <v>8.18454008738521E-2</v>
       </c>
-      <c r="AM23">
+      <c r="AM23" s="3">
         <v>3.7098166666666659</v>
       </c>
-      <c r="AN23">
+      <c r="AN23" s="3">
         <v>268.67007159465919</v>
       </c>
-      <c r="AO23">
+      <c r="AO23" s="3">
         <v>5.8273088980983302E-2</v>
       </c>
-      <c r="AP23">
+      <c r="AP23" s="3">
         <v>7.14768141689755E-2</v>
       </c>
-      <c r="AQ23">
+      <c r="AQ23" s="3">
         <v>7.5806284262337403E-2</v>
       </c>
-      <c r="AR23">
+      <c r="AR23" s="3">
         <v>0.1202252283014707</v>
       </c>
-      <c r="AS23">
+      <c r="AS23" s="3">
         <v>0.1304116900408093</v>
       </c>
-      <c r="AU23">
+      <c r="AU23" s="2">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="AV23">
+      <c r="AV23" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -7145,147 +7152,147 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:48" x14ac:dyDescent="0.2">
-      <c r="A45" t="s">
+    <row r="45" spans="1:48" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B45" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C45" t="s">
+      <c r="C45" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D45">
+      <c r="D45" s="3">
         <v>1.6666666666666601E-2</v>
       </c>
-      <c r="E45">
+      <c r="E45" s="3">
         <v>0.41666666666666669</v>
       </c>
-      <c r="F45">
+      <c r="F45" s="3">
         <v>1.3003859749673901E-2</v>
       </c>
-      <c r="G45">
+      <c r="G45" s="3">
         <v>109.89353143042651</v>
       </c>
-      <c r="H45">
+      <c r="H45" s="3">
         <v>-2.3902777776309501</v>
       </c>
-      <c r="I45">
+      <c r="I45" s="3">
         <v>0.99768518535332762</v>
       </c>
-      <c r="J45">
+      <c r="J45" s="3">
         <v>-0.52067049446490854</v>
       </c>
-      <c r="K45">
+      <c r="K45" s="3">
         <v>-3.3069444442967781</v>
       </c>
-      <c r="L45">
+      <c r="L45" s="3">
         <v>9.3055555724170805E-2</v>
       </c>
-      <c r="M45">
+      <c r="M45" s="3">
         <v>-2.7069444442973229</v>
       </c>
-      <c r="N45">
+      <c r="N45" s="3">
         <v>1.3319444446119331</v>
       </c>
-      <c r="O45">
+      <c r="O45" s="3">
         <v>3.651288681874731</v>
       </c>
-      <c r="P45">
+      <c r="P45" s="3">
         <v>7.8787318350159993E-2</v>
       </c>
-      <c r="Q45">
+      <c r="Q45" s="3">
         <v>-1.4600171611255699E-2</v>
       </c>
-      <c r="R45">
+      <c r="R45" s="3">
         <v>-1.23039137519969E-2</v>
       </c>
-      <c r="S45">
+      <c r="S45" s="3">
         <v>1.3003790827902199E-2</v>
       </c>
-      <c r="T45">
+      <c r="T45" s="3">
         <v>80.236743564066686</v>
       </c>
-      <c r="U45">
+      <c r="U45" s="3">
         <v>-2.1513888887422179</v>
       </c>
-      <c r="V45">
+      <c r="V45" s="3">
         <v>0.79328703720352922</v>
       </c>
-      <c r="W45">
+      <c r="W45" s="3">
         <v>-0.54897613944155765</v>
       </c>
-      <c r="X45">
+      <c r="X45" s="3">
         <v>-3.0680555554080451</v>
       </c>
-      <c r="Y45">
+      <c r="Y45" s="3">
         <v>-3.4722222054976201E-2</v>
       </c>
-      <c r="Z45">
+      <c r="Z45" s="3">
         <v>-1.5083333331872451</v>
       </c>
-      <c r="AA45">
+      <c r="AA45" s="3">
         <v>1.4291666668325891</v>
       </c>
-      <c r="AB45">
+      <c r="AB45" s="3">
         <v>3.0485309828600009</v>
       </c>
-      <c r="AC45">
+      <c r="AC45" s="3">
         <v>-1.2303983412203999E-2</v>
       </c>
-      <c r="AD45">
+      <c r="AD45" s="3">
         <v>2.7533873633457131</v>
       </c>
-      <c r="AE45">
+      <c r="AE45" s="3">
         <v>3.0612556299293381</v>
       </c>
-      <c r="AF45">
+      <c r="AF45" s="3">
         <v>3.495036927861916</v>
       </c>
-      <c r="AG45">
+      <c r="AG45" s="3">
         <v>3.9086136252326211</v>
       </c>
-      <c r="AH45">
+      <c r="AH45" s="3">
         <v>1.210866194903776</v>
       </c>
-      <c r="AI45">
+      <c r="AI45" s="3">
         <v>15.278333333333331</v>
       </c>
-      <c r="AJ45">
+      <c r="AJ45" s="3">
         <v>15.12833333333333</v>
       </c>
-      <c r="AK45">
+      <c r="AK45" s="3">
         <v>0.8441809455723881</v>
       </c>
-      <c r="AL45">
+      <c r="AL45" s="3">
         <v>0.85749184750213281</v>
       </c>
-      <c r="AM45">
+      <c r="AM45" s="3">
         <v>3.5649000000000002</v>
       </c>
-      <c r="AN45">
+      <c r="AN45" s="3">
         <v>188.89512640498901</v>
       </c>
-      <c r="AO45">
+      <c r="AO45" s="3">
         <v>7.0159062213749304E-2</v>
       </c>
-      <c r="AP45">
+      <c r="AP45" s="3">
         <v>6.6211304738359303E-2</v>
       </c>
-      <c r="AQ45">
+      <c r="AQ45" s="3">
         <v>6.7718600255146699E-2</v>
       </c>
-      <c r="AR45">
+      <c r="AR45" s="3">
         <v>8.6604944217169605E-2</v>
       </c>
-      <c r="AS45">
+      <c r="AS45" s="3">
         <v>9.3497722659340504E-2</v>
       </c>
-      <c r="AU45">
+      <c r="AU45" s="2">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="AV45">
+      <c r="AV45" s="2">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -7725,7 +7732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>102</v>
       </c>
@@ -7869,8 +7876,11 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
+      <c r="AX49" s="3" t="s">
+        <v>117</v>
+      </c>
     </row>
-    <row r="50" spans="1:48" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:50" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>103</v>
       </c>
@@ -8015,7 +8025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:48" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:50" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>104</v>
       </c>
@@ -8160,7 +8170,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:48" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:50" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>106</v>
       </c>
@@ -8305,7 +8315,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:48" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:50" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>107</v>
       </c>
@@ -8450,7 +8460,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:48" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:50" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>108</v>
       </c>
@@ -8595,7 +8605,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>109</v>
       </c>
@@ -8740,152 +8750,155 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:48" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A56" t="s">
+    <row r="56" spans="1:50" s="3" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B56" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="C56" t="s">
+      <c r="C56" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D56">
+      <c r="D56" s="3">
         <v>29.55</v>
       </c>
-      <c r="E56">
+      <c r="E56" s="3">
         <v>69.75</v>
       </c>
-      <c r="F56">
+      <c r="F56" s="3">
         <v>-8.4632034546076994E-3</v>
       </c>
-      <c r="G56">
+      <c r="G56" s="3">
         <v>92.454341048082199</v>
       </c>
-      <c r="H56">
+      <c r="H56" s="3">
         <v>1.1027777779214181</v>
       </c>
-      <c r="I56">
+      <c r="I56" s="3">
         <v>0.3576388890578982</v>
       </c>
-      <c r="J56">
+      <c r="J56" s="3">
         <v>0.46751159736099529</v>
       </c>
-      <c r="K56">
+      <c r="K56" s="3">
         <v>0.68750000014401846</v>
       </c>
-      <c r="L56">
+      <c r="L56" s="3">
         <v>0.1791666668353552</v>
       </c>
-      <c r="M56">
+      <c r="M56" s="3">
         <v>0.98750000014374562</v>
       </c>
-      <c r="N56">
+      <c r="N56" s="3">
         <v>0.1791666668353552</v>
       </c>
-      <c r="O56">
+      <c r="O56" s="3">
         <v>3.2074564938710881</v>
       </c>
-      <c r="P56">
+      <c r="P56" s="3">
         <v>4.6312528349533102E-2</v>
       </c>
-      <c r="Q56">
+      <c r="Q56" s="3">
         <v>2.17239108363045E-2</v>
       </c>
-      <c r="R56">
+      <c r="R56" s="3">
         <v>6.3121497629772998E-3</v>
       </c>
-      <c r="S56">
+      <c r="S56" s="3">
         <v>-8.4632723763794007E-3</v>
       </c>
-      <c r="T56">
+      <c r="T56" s="3">
         <v>26.256275952752539</v>
       </c>
-      <c r="U56">
+      <c r="U56" s="3">
         <v>1.3416666668101509</v>
       </c>
-      <c r="V56">
+      <c r="V56" s="3">
         <v>5.1388889056064001E-2</v>
       </c>
-      <c r="W56">
+      <c r="W56" s="3">
         <v>0.40309829075708931</v>
       </c>
-      <c r="X56">
+      <c r="X56" s="3">
         <v>0.92638888903275085</v>
       </c>
-      <c r="Y56">
+      <c r="Y56" s="3">
         <v>5.1388889056064001E-2</v>
       </c>
-      <c r="Z56">
+      <c r="Z56" s="3">
         <v>1.7569444445875511</v>
       </c>
-      <c r="AA56">
+      <c r="AA56" s="3">
         <v>5.1388889056064001E-2</v>
       </c>
-      <c r="AB56">
+      <c r="AB56" s="3">
         <v>2.5194444444424651</v>
       </c>
-      <c r="AC56">
+      <c r="AC56" s="3">
         <v>6.3120801027701998E-3</v>
       </c>
-      <c r="AD56">
+      <c r="AD56" s="3">
         <v>5.1149002166389979</v>
       </c>
-      <c r="AE56">
+      <c r="AE56" s="3">
         <v>4.7494454764661818</v>
       </c>
-      <c r="AF56">
+      <c r="AF56" s="3">
         <v>4.9014676997013851</v>
       </c>
-      <c r="AG56">
+      <c r="AG56" s="3">
         <v>5.7287111558806121</v>
       </c>
-      <c r="AH56">
+      <c r="AH56" s="3">
         <v>0.2517182942385438</v>
       </c>
-      <c r="AI56">
+      <c r="AI56" s="3">
         <v>13.57666666666667</v>
       </c>
-      <c r="AJ56">
+      <c r="AJ56" s="3">
         <v>13.526666666666671</v>
       </c>
-      <c r="AK56">
+      <c r="AK56" s="3">
         <v>1.4313050178430999E-3</v>
       </c>
-      <c r="AL56">
+      <c r="AL56" s="3">
         <v>1.82518087329453E-2</v>
       </c>
-      <c r="AM56">
+      <c r="AM56" s="3">
         <v>1.6092166666666661</v>
       </c>
-      <c r="AN56">
+      <c r="AN56" s="3">
         <v>35.240561193396132</v>
       </c>
-      <c r="AO56">
+      <c r="AO56" s="3">
         <v>8.0495184136264705E-2</v>
       </c>
-      <c r="AP56">
+      <c r="AP56" s="3">
         <v>6.5224267927405905E-2</v>
       </c>
-      <c r="AQ56">
+      <c r="AQ56" s="3">
         <v>6.5945858715738104E-2</v>
       </c>
-      <c r="AR56">
+      <c r="AR56" s="3">
         <v>8.7849450139929994E-2</v>
       </c>
-      <c r="AS56">
+      <c r="AS56" s="3">
         <v>9.5058952792500304E-2</v>
       </c>
-      <c r="AU56" s="2">
+      <c r="AU56" s="3">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="AV56" s="2">
+      <c r="AV56" s="3">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
+      <c r="AX56" s="3" t="s">
+        <v>117</v>
+      </c>
     </row>
-    <row r="57" spans="1:48" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:50" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>111</v>
       </c>
@@ -9030,7 +9043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:48" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:50" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>112</v>
       </c>
@@ -9175,7 +9188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>113</v>
       </c>
@@ -9320,7 +9333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:48" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:50" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>115</v>
       </c>
@@ -9465,7 +9478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:48" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:50" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>116</v>
       </c>
